--- a/translate/VMSTools.xlsx
+++ b/translate/VMSTools.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="586">
   <si>
     <t>英文（en_US）</t>
   </si>
@@ -328,6 +328,12 @@
     <t>NTP Port</t>
   </si>
   <si>
+    <t>NTP端口输入值需在0或1~65535区间</t>
+  </si>
+  <si>
+    <t>NTP port value must be 0 or within the range 1–65535</t>
+  </si>
+  <si>
     <t>OSD修改</t>
   </si>
   <si>
@@ -409,6 +415,12 @@
     <t>Mar.</t>
   </si>
   <si>
+    <t>上传完成, 等待设备重启生效...</t>
+  </si>
+  <si>
+    <t>Upload complete. Waiting for the device to restart for changes to take effect...</t>
+  </si>
+  <si>
     <t>上传配置文件</t>
   </si>
   <si>
@@ -580,6 +592,12 @@
     <t>Refresh Interval</t>
   </si>
   <si>
+    <t>刷新间隔输入值需在0或60~999999区间</t>
+  </si>
+  <si>
+    <t>Refresh interval value must be 0 or within the range 60–999999</t>
+  </si>
+  <si>
     <t>十一月份</t>
   </si>
   <si>
@@ -604,12 +622,24 @@
     <t>Upgraded Version Number</t>
   </si>
   <si>
+    <t>升级失败</t>
+  </si>
+  <si>
+    <t>Upgrade failed</t>
+  </si>
+  <si>
     <t>升级当前版本号</t>
   </si>
   <si>
     <t>Current Version Number</t>
   </si>
   <si>
+    <t>升级成功</t>
+  </si>
+  <si>
+    <t>Upgrade successful</t>
+  </si>
+  <si>
     <t>升级文件</t>
   </si>
   <si>
@@ -769,10 +799,10 @@
     <t>DST End Datetime</t>
   </si>
   <si>
-    <t>失败(已跳过)</t>
-  </si>
-  <si>
-    <t>Failure(Skipped)</t>
+    <t>失败</t>
+  </si>
+  <si>
+    <t>Failed</t>
   </si>
   <si>
     <t>媒体设置</t>
@@ -859,6 +889,12 @@
     <t>%1 devices playing. Close idle streams to continue.</t>
   </si>
   <si>
+    <t>当前已是最新版本!</t>
+  </si>
+  <si>
+    <t>Already on the latest version!</t>
+  </si>
+  <si>
     <t>当前有%1台设备正在直播, 确定要关闭吗?</t>
   </si>
   <si>
@@ -871,12 +907,24 @@
     <t>%1 devices streaming. Close and exit?</t>
   </si>
   <si>
+    <t>当前选择版本过低!</t>
+  </si>
+  <si>
+    <t>The selected version is too old!</t>
+  </si>
+  <si>
     <t>心跳周期</t>
   </si>
   <si>
     <t>Heartbeat Cyde</t>
   </si>
   <si>
+    <t>总共%1台设备, 成功%2台, 失败%3台</t>
+  </si>
+  <si>
+    <t>Total: %1 devices — %2 succeeded, %3 failed</t>
+  </si>
+  <si>
     <t>恢复出厂设置</t>
   </si>
   <si>
@@ -1153,6 +1201,12 @@
     <t>Title Message (^split mylti-line)</t>
   </si>
   <si>
+    <t>正在上传固件...</t>
+  </si>
+  <si>
+    <t>Uploading firmware...</t>
+  </si>
+  <si>
     <t>正在分配空闲IP...</t>
   </si>
   <si>
@@ -1177,6 +1231,18 @@
     <t>Exiting...</t>
   </si>
   <si>
+    <t>正在重启设备...</t>
+  </si>
+  <si>
+    <t>Restarting device...</t>
+  </si>
+  <si>
+    <t>正在重置设备...</t>
+  </si>
+  <si>
+    <t>Resetting device...</t>
+  </si>
+  <si>
     <t>每天</t>
   </si>
   <si>
@@ -1387,12 +1453,6 @@
     <t>Network card</t>
   </si>
   <si>
-    <t>网段内空闲IP不足(需%1个, 只找到%2个), 请调整起始IP</t>
-  </si>
-  <si>
-    <t>Not enough free IPs (need %1, found %2). Adjust start IP.</t>
-  </si>
-  <si>
     <t>网络参数</t>
   </si>
   <si>
@@ -1477,6 +1537,12 @@
     <t>Deivces Languagers</t>
   </si>
   <si>
+    <t>设备重启</t>
+  </si>
+  <si>
+    <t>Restart Device</t>
+  </si>
+  <si>
     <t>设定IP</t>
   </si>
   <si>
@@ -1612,10 +1678,10 @@
     <t>Please select the device first. Do you choose all devices?</t>
   </si>
   <si>
-    <t>请选择 %1 升级文件（可多选）</t>
-  </si>
-  <si>
-    <t>Select %1 firmware file(s)</t>
+    <t>请选择 %1 升级文件</t>
+  </si>
+  <si>
+    <t>Please select %1 upgrade file(s)</t>
   </si>
   <si>
     <t>请选择升级文件</t>
@@ -1631,6 +1697,12 @@
   </si>
   <si>
     <t>Account Manage</t>
+  </si>
+  <si>
+    <t>起始IP后续可用IP不足, 批量分配失败, 请更换起始IP, 减少设备或更换网段</t>
+  </si>
+  <si>
+    <t>Not enough available IP addresses after the starting IP. Batch assignment failed. Please change the starting IP, reduce the number of devices, or use a different subnet.</t>
   </si>
   <si>
     <t>连接中...</t>
@@ -1730,7 +1802,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1761,6 +1833,13 @@
       <sz val="12"/>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -2264,16 +2343,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2282,119 +2358,122 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2416,6 +2495,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3721,7 +3803,7 @@
         <v>104</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
@@ -3735,13 +3817,13 @@
     </row>
     <row r="45" ht="30" customHeight="1" spans="1:18">
       <c r="A45" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
@@ -4001,7 +4083,7 @@
         <v>131</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D58" s="7"/>
       <c r="E58" s="7"/>
@@ -4015,13 +4097,13 @@
     </row>
     <row r="59" ht="30" customHeight="1" spans="1:18">
       <c r="A59" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D59" s="7"/>
       <c r="E59" s="7"/>
@@ -4035,13 +4117,13 @@
     </row>
     <row r="60" ht="30" customHeight="1" spans="1:18">
       <c r="A60" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C60" s="7" t="s">
         <v>134</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>135</v>
       </c>
       <c r="D60" s="7"/>
       <c r="E60" s="7"/>
@@ -4660,7 +4742,7 @@
       <c r="B91" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="C91" s="7" t="s">
+      <c r="C91" s="8" t="s">
         <v>197</v>
       </c>
       <c r="D91" s="7"/>
@@ -4700,7 +4782,7 @@
       <c r="B93" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="C93" s="7" t="s">
+      <c r="C93" s="8" t="s">
         <v>201</v>
       </c>
       <c r="D93" s="7"/>
@@ -4741,7 +4823,7 @@
         <v>204</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="D95" s="7"/>
       <c r="E95" s="7"/>
@@ -4755,13 +4837,13 @@
     </row>
     <row r="96" ht="30" customHeight="1" spans="1:18">
       <c r="A96" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D96" s="7"/>
       <c r="E96" s="7"/>
@@ -4775,13 +4857,13 @@
     </row>
     <row r="97" ht="30" customHeight="1" spans="1:18">
       <c r="A97" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D97" s="7"/>
       <c r="E97" s="7"/>
@@ -4795,13 +4877,13 @@
     </row>
     <row r="98" ht="30" customHeight="1" spans="1:18">
       <c r="A98" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D98" s="7"/>
       <c r="E98" s="7"/>
@@ -4815,13 +4897,13 @@
     </row>
     <row r="99" ht="30" customHeight="1" spans="1:18">
       <c r="A99" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D99" s="7"/>
       <c r="E99" s="7"/>
@@ -4835,13 +4917,13 @@
     </row>
     <row r="100" ht="30" customHeight="1" spans="1:18">
       <c r="A100" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>214</v>
+        <v>181</v>
       </c>
       <c r="D100" s="7"/>
       <c r="E100" s="7"/>
@@ -6821,7 +6903,7 @@
         <v>411</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>208</v>
+        <v>412</v>
       </c>
       <c r="D199" s="7"/>
       <c r="E199" s="7"/>
@@ -6835,13 +6917,13 @@
     </row>
     <row r="200" ht="30" customHeight="1" spans="1:18">
       <c r="A200" s="7" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C200" s="7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D200" s="7"/>
       <c r="E200" s="7"/>
@@ -6855,13 +6937,13 @@
     </row>
     <row r="201" ht="30" customHeight="1" spans="1:18">
       <c r="A201" s="7" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D201" s="7"/>
       <c r="E201" s="7"/>
@@ -6875,13 +6957,13 @@
     </row>
     <row r="202" ht="30" customHeight="1" spans="1:18">
       <c r="A202" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C202" s="7" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D202" s="7"/>
       <c r="E202" s="7"/>
@@ -6895,13 +6977,13 @@
     </row>
     <row r="203" ht="30" customHeight="1" spans="1:18">
       <c r="A203" s="7" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>130</v>
+        <v>420</v>
       </c>
       <c r="D203" s="7"/>
       <c r="E203" s="7"/>
@@ -6915,13 +6997,13 @@
     </row>
     <row r="204" ht="30" customHeight="1" spans="1:18">
       <c r="A204" s="7" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D204" s="7"/>
       <c r="E204" s="7"/>
@@ -6935,13 +7017,13 @@
     </row>
     <row r="205" ht="30" customHeight="1" spans="1:18">
       <c r="A205" s="7" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C205" s="7" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D205" s="7"/>
       <c r="E205" s="7"/>
@@ -6955,13 +7037,13 @@
     </row>
     <row r="206" ht="30" customHeight="1" spans="1:18">
       <c r="A206" s="7" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C206" s="7" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D206" s="7"/>
       <c r="E206" s="7"/>
@@ -6975,13 +7057,13 @@
     </row>
     <row r="207" ht="30" customHeight="1" spans="1:18">
       <c r="A207" s="7" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C207" s="7" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D207" s="7"/>
       <c r="E207" s="7"/>
@@ -6995,13 +7077,13 @@
     </row>
     <row r="208" ht="30" customHeight="1" spans="1:18">
       <c r="A208" s="7" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C208" s="7" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D208" s="7"/>
       <c r="E208" s="7"/>
@@ -7015,13 +7097,13 @@
     </row>
     <row r="209" ht="30" customHeight="1" spans="1:18">
       <c r="A209" s="7" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C209" s="7" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D209" s="7"/>
       <c r="E209" s="7"/>
@@ -7035,13 +7117,13 @@
     </row>
     <row r="210" ht="30" customHeight="1" spans="1:18">
       <c r="A210" s="7" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B210" s="7" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C210" s="7" t="s">
-        <v>432</v>
+        <v>218</v>
       </c>
       <c r="D210" s="7"/>
       <c r="E210" s="7"/>
@@ -7055,13 +7137,13 @@
     </row>
     <row r="211" ht="30" customHeight="1" spans="1:18">
       <c r="A211" s="7" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B211" s="7" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C211" s="7" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D211" s="7"/>
       <c r="E211" s="7"/>
@@ -7075,13 +7157,13 @@
     </row>
     <row r="212" ht="30" customHeight="1" spans="1:18">
       <c r="A212" s="7" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B212" s="7" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C212" s="7" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D212" s="7"/>
       <c r="E212" s="7"/>
@@ -7095,13 +7177,13 @@
     </row>
     <row r="213" ht="30" customHeight="1" spans="1:18">
       <c r="A213" s="7" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B213" s="7" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C213" s="7" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D213" s="7"/>
       <c r="E213" s="7"/>
@@ -7115,13 +7197,13 @@
     </row>
     <row r="214" ht="30" customHeight="1" spans="1:18">
       <c r="A214" s="7" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B214" s="7" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C214" s="7" t="s">
-        <v>440</v>
+        <v>134</v>
       </c>
       <c r="D214" s="7"/>
       <c r="E214" s="7"/>
@@ -7621,7 +7703,7 @@
         <v>489</v>
       </c>
       <c r="C239" s="7" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="D239" s="7"/>
       <c r="E239" s="7"/>
@@ -7635,13 +7717,13 @@
     </row>
     <row r="240" ht="30" customHeight="1" spans="1:18">
       <c r="A240" s="7" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B240" s="7" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C240" s="7" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D240" s="7"/>
       <c r="E240" s="7"/>
@@ -7655,13 +7737,13 @@
     </row>
     <row r="241" ht="30" customHeight="1" spans="1:18">
       <c r="A241" s="7" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B241" s="7" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C241" s="7" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D241" s="7"/>
       <c r="E241" s="7"/>
@@ -7675,13 +7757,13 @@
     </row>
     <row r="242" ht="30" customHeight="1" spans="1:18">
       <c r="A242" s="7" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B242" s="7" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C242" s="7" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D242" s="7"/>
       <c r="E242" s="7"/>
@@ -7695,13 +7777,13 @@
     </row>
     <row r="243" ht="30" customHeight="1" spans="1:18">
       <c r="A243" s="7" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B243" s="7" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C243" s="7" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D243" s="7"/>
       <c r="E243" s="7"/>
@@ -7715,13 +7797,13 @@
     </row>
     <row r="244" ht="30" customHeight="1" spans="1:18">
       <c r="A244" s="7" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B244" s="7" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C244" s="7" t="s">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="D244" s="7"/>
       <c r="E244" s="7"/>
@@ -7735,13 +7817,13 @@
     </row>
     <row r="245" ht="30" customHeight="1" spans="1:18">
       <c r="A245" s="7" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B245" s="7" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C245" s="7" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D245" s="7"/>
       <c r="E245" s="7"/>
@@ -7755,13 +7837,13 @@
     </row>
     <row r="246" ht="30" customHeight="1" spans="1:18">
       <c r="A246" s="7" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B246" s="7" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C246" s="7" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D246" s="7"/>
       <c r="E246" s="7"/>
@@ -7775,13 +7857,13 @@
     </row>
     <row r="247" ht="30" customHeight="1" spans="1:18">
       <c r="A247" s="7" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B247" s="7" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C247" s="7" t="s">
-        <v>464</v>
+        <v>506</v>
       </c>
       <c r="D247" s="7"/>
       <c r="E247" s="7"/>
@@ -7795,13 +7877,13 @@
     </row>
     <row r="248" ht="30" customHeight="1" spans="1:18">
       <c r="A248" s="7" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B248" s="7" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C248" s="7" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="D248" s="7"/>
       <c r="E248" s="7"/>
@@ -7815,13 +7897,13 @@
     </row>
     <row r="249" ht="30" customHeight="1" spans="1:18">
       <c r="A249" s="7" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B249" s="7" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C249" s="7" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D249" s="7"/>
       <c r="E249" s="7"/>
@@ -7835,13 +7917,13 @@
     </row>
     <row r="250" ht="30" customHeight="1" spans="1:18">
       <c r="A250" s="7" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B250" s="7" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C250" s="7" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="D250" s="7"/>
       <c r="E250" s="7"/>
@@ -7855,13 +7937,13 @@
     </row>
     <row r="251" ht="30" customHeight="1" spans="1:18">
       <c r="A251" s="7" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B251" s="7" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C251" s="7" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D251" s="7"/>
       <c r="E251" s="7"/>
@@ -7875,13 +7957,13 @@
     </row>
     <row r="252" ht="30" customHeight="1" spans="1:18">
       <c r="A252" s="7" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B252" s="7" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C252" s="7" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D252" s="7"/>
       <c r="E252" s="7"/>
@@ -7895,13 +7977,13 @@
     </row>
     <row r="253" ht="30" customHeight="1" spans="1:18">
       <c r="A253" s="7" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B253" s="7" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C253" s="7" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D253" s="7"/>
       <c r="E253" s="7"/>
@@ -7915,13 +7997,13 @@
     </row>
     <row r="254" ht="30" customHeight="1" spans="1:18">
       <c r="A254" s="7" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B254" s="7" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C254" s="7" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D254" s="7"/>
       <c r="E254" s="7"/>
@@ -7935,13 +8017,13 @@
     </row>
     <row r="255" ht="30" customHeight="1" spans="1:18">
       <c r="A255" s="7" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B255" s="7" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C255" s="7" t="s">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="D255" s="7"/>
       <c r="E255" s="7"/>
@@ -7955,13 +8037,13 @@
     </row>
     <row r="256" ht="30" customHeight="1" spans="1:18">
       <c r="A256" s="7" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B256" s="7" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C256" s="7" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D256" s="7"/>
       <c r="E256" s="7"/>
@@ -7975,13 +8057,13 @@
     </row>
     <row r="257" ht="30" customHeight="1" spans="1:18">
       <c r="A257" s="7" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B257" s="7" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C257" s="7" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D257" s="7"/>
       <c r="E257" s="7"/>
@@ -7995,13 +8077,13 @@
     </row>
     <row r="258" ht="30" customHeight="1" spans="1:18">
       <c r="A258" s="7" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B258" s="7" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C258" s="7" t="s">
-        <v>525</v>
+        <v>484</v>
       </c>
       <c r="D258" s="7"/>
       <c r="E258" s="7"/>
@@ -8041,7 +8123,7 @@
         <v>528</v>
       </c>
       <c r="C260" s="7" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="D260" s="7"/>
       <c r="E260" s="7"/>
@@ -8055,13 +8137,13 @@
     </row>
     <row r="261" ht="30" customHeight="1" spans="1:18">
       <c r="A261" s="7" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B261" s="7" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C261" s="7" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D261" s="7"/>
       <c r="E261" s="7"/>
@@ -8075,13 +8157,13 @@
     </row>
     <row r="262" ht="30" customHeight="1" spans="1:18">
       <c r="A262" s="7" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B262" s="7" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C262" s="7" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D262" s="7"/>
       <c r="E262" s="7"/>
@@ -8095,13 +8177,13 @@
     </row>
     <row r="263" ht="30" customHeight="1" spans="1:18">
       <c r="A263" s="7" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B263" s="7" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C263" s="7" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D263" s="7"/>
       <c r="E263" s="7"/>
@@ -8115,13 +8197,13 @@
     </row>
     <row r="264" ht="30" customHeight="1" spans="1:18">
       <c r="A264" s="7" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B264" s="7" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C264" s="7" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D264" s="7"/>
       <c r="E264" s="7"/>
@@ -8135,13 +8217,13 @@
     </row>
     <row r="265" ht="30" customHeight="1" spans="1:18">
       <c r="A265" s="7" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B265" s="7" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C265" s="7" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D265" s="7"/>
       <c r="E265" s="7"/>
@@ -8155,13 +8237,13 @@
     </row>
     <row r="266" ht="30" customHeight="1" spans="1:18">
       <c r="A266" s="7" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B266" s="7" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C266" s="7" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D266" s="7"/>
       <c r="E266" s="7"/>
@@ -8175,13 +8257,13 @@
     </row>
     <row r="267" ht="30" customHeight="1" spans="1:18">
       <c r="A267" s="7" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B267" s="7" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C267" s="7" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D267" s="7"/>
       <c r="E267" s="7"/>
@@ -8195,13 +8277,13 @@
     </row>
     <row r="268" ht="30" customHeight="1" spans="1:18">
       <c r="A268" s="7" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B268" s="7" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C268" s="7" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D268" s="7"/>
       <c r="E268" s="7"/>
@@ -8215,13 +8297,13 @@
     </row>
     <row r="269" ht="30" customHeight="1" spans="1:18">
       <c r="A269" s="7" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B269" s="7" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C269" s="7" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D269" s="7"/>
       <c r="E269" s="7"/>
@@ -8235,13 +8317,13 @@
     </row>
     <row r="270" ht="30" customHeight="1" spans="1:18">
       <c r="A270" s="7" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B270" s="7" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C270" s="7" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D270" s="7"/>
       <c r="E270" s="7"/>
@@ -8255,13 +8337,13 @@
     </row>
     <row r="271" ht="30" customHeight="1" spans="1:18">
       <c r="A271" s="7" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B271" s="7" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C271" s="7" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="D271" s="7"/>
       <c r="E271" s="7"/>
@@ -8301,7 +8383,7 @@
         <v>553</v>
       </c>
       <c r="C273" s="7" t="s">
-        <v>511</v>
+        <v>554</v>
       </c>
       <c r="D273" s="7"/>
       <c r="E273" s="7"/>
@@ -8315,13 +8397,13 @@
     </row>
     <row r="274" ht="30" customHeight="1" spans="1:18">
       <c r="A274" s="7" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B274" s="7" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C274" s="7" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D274" s="7"/>
       <c r="E274" s="7"/>
@@ -8335,13 +8417,13 @@
     </row>
     <row r="275" ht="30" customHeight="1" spans="1:18">
       <c r="A275" s="7" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B275" s="7" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C275" s="7" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D275" s="7"/>
       <c r="E275" s="7"/>
@@ -8355,13 +8437,13 @@
     </row>
     <row r="276" ht="30" customHeight="1" spans="1:18">
       <c r="A276" s="7" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B276" s="7" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C276" s="7" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D276" s="7"/>
       <c r="E276" s="7"/>
@@ -8375,13 +8457,13 @@
     </row>
     <row r="277" ht="30" customHeight="1" spans="1:18">
       <c r="A277" s="7" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B277" s="7" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C277" s="7" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D277" s="7"/>
       <c r="E277" s="7"/>
@@ -8394,9 +8476,15 @@
       <c r="R277" s="7"/>
     </row>
     <row r="278" ht="30" customHeight="1" spans="1:18">
-      <c r="A278" s="7"/>
-      <c r="B278" s="7"/>
-      <c r="C278" s="7"/>
+      <c r="A278" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="B278" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="C278" s="7" t="s">
+        <v>564</v>
+      </c>
       <c r="D278" s="7"/>
       <c r="E278" s="7"/>
       <c r="F278" s="7"/>
@@ -8408,9 +8496,15 @@
       <c r="R278" s="7"/>
     </row>
     <row r="279" ht="30" customHeight="1" spans="1:18">
-      <c r="A279" s="7"/>
-      <c r="B279" s="7"/>
-      <c r="C279" s="7"/>
+      <c r="A279" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="B279" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="C279" s="7" t="s">
+        <v>566</v>
+      </c>
       <c r="D279" s="7"/>
       <c r="E279" s="7"/>
       <c r="F279" s="7"/>
@@ -8422,9 +8516,15 @@
       <c r="R279" s="7"/>
     </row>
     <row r="280" ht="30" customHeight="1" spans="1:18">
-      <c r="A280" s="7"/>
-      <c r="B280" s="7"/>
-      <c r="C280" s="7"/>
+      <c r="A280" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="B280" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="C280" s="7" t="s">
+        <v>568</v>
+      </c>
       <c r="D280" s="7"/>
       <c r="E280" s="7"/>
       <c r="F280" s="7"/>
@@ -8436,9 +8536,15 @@
       <c r="R280" s="7"/>
     </row>
     <row r="281" ht="30" customHeight="1" spans="1:18">
-      <c r="A281" s="7"/>
-      <c r="B281" s="7"/>
-      <c r="C281" s="7"/>
+      <c r="A281" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="B281" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="C281" s="7" t="s">
+        <v>570</v>
+      </c>
       <c r="D281" s="7"/>
       <c r="E281" s="7"/>
       <c r="F281" s="7"/>
@@ -8450,9 +8556,15 @@
       <c r="R281" s="7"/>
     </row>
     <row r="282" ht="30" customHeight="1" spans="1:18">
-      <c r="A282" s="7"/>
-      <c r="B282" s="7"/>
-      <c r="C282" s="7"/>
+      <c r="A282" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="B282" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="C282" s="7" t="s">
+        <v>572</v>
+      </c>
       <c r="D282" s="7"/>
       <c r="E282" s="7"/>
       <c r="F282" s="7"/>
@@ -8464,9 +8576,15 @@
       <c r="R282" s="7"/>
     </row>
     <row r="283" ht="30" customHeight="1" spans="1:18">
-      <c r="A283" s="7"/>
-      <c r="B283" s="7"/>
-      <c r="C283" s="7"/>
+      <c r="A283" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="B283" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="C283" s="7" t="s">
+        <v>574</v>
+      </c>
       <c r="D283" s="7"/>
       <c r="E283" s="7"/>
       <c r="F283" s="7"/>
@@ -8478,9 +8596,15 @@
       <c r="R283" s="7"/>
     </row>
     <row r="284" ht="30" customHeight="1" spans="1:18">
-      <c r="A284" s="7"/>
-      <c r="B284" s="7"/>
-      <c r="C284" s="7"/>
+      <c r="A284" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="B284" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="C284" s="7" t="s">
+        <v>576</v>
+      </c>
       <c r="D284" s="7"/>
       <c r="E284" s="7"/>
       <c r="F284" s="7"/>
@@ -8492,9 +8616,15 @@
       <c r="R284" s="7"/>
     </row>
     <row r="285" ht="30" customHeight="1" spans="1:18">
-      <c r="A285" s="7"/>
-      <c r="B285" s="7"/>
-      <c r="C285" s="7"/>
+      <c r="A285" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="B285" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="C285" s="7" t="s">
+        <v>533</v>
+      </c>
       <c r="D285" s="7"/>
       <c r="E285" s="7"/>
       <c r="F285" s="7"/>
@@ -8506,9 +8636,15 @@
       <c r="R285" s="7"/>
     </row>
     <row r="286" ht="30" customHeight="1" spans="1:18">
-      <c r="A286" s="7"/>
-      <c r="B286" s="7"/>
-      <c r="C286" s="7"/>
+      <c r="A286" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="B286" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="C286" s="7" t="s">
+        <v>579</v>
+      </c>
       <c r="D286" s="7"/>
       <c r="E286" s="7"/>
       <c r="F286" s="7"/>
@@ -8520,9 +8656,15 @@
       <c r="R286" s="7"/>
     </row>
     <row r="287" ht="30" customHeight="1" spans="1:18">
-      <c r="A287" s="7"/>
-      <c r="B287" s="7"/>
-      <c r="C287" s="7"/>
+      <c r="A287" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="B287" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="C287" s="7" t="s">
+        <v>581</v>
+      </c>
       <c r="D287" s="7"/>
       <c r="E287" s="7"/>
       <c r="F287" s="7"/>
@@ -8534,9 +8676,15 @@
       <c r="R287" s="7"/>
     </row>
     <row r="288" ht="30" customHeight="1" spans="1:18">
-      <c r="A288" s="7"/>
-      <c r="B288" s="7"/>
-      <c r="C288" s="7"/>
+      <c r="A288" s="7" t="s">
+        <v>582</v>
+      </c>
+      <c r="B288" s="7" t="s">
+        <v>582</v>
+      </c>
+      <c r="C288" s="7" t="s">
+        <v>583</v>
+      </c>
       <c r="D288" s="7"/>
       <c r="E288" s="7"/>
       <c r="F288" s="7"/>
@@ -8548,9 +8696,15 @@
       <c r="R288" s="7"/>
     </row>
     <row r="289" ht="30" customHeight="1" spans="1:18">
-      <c r="A289" s="7"/>
-      <c r="B289" s="7"/>
-      <c r="C289" s="7"/>
+      <c r="A289" s="7" t="s">
+        <v>584</v>
+      </c>
+      <c r="B289" s="7" t="s">
+        <v>584</v>
+      </c>
+      <c r="C289" s="7" t="s">
+        <v>585</v>
+      </c>
       <c r="D289" s="7"/>
       <c r="E289" s="7"/>
       <c r="F289" s="7"/>
